--- a/wiki/reports/daily/2026-10-23_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-23_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,17 +71,22 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,17 +100,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F7"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FADBD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,11 +116,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -190,37 +185,31 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -588,10 +577,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -605,14 +594,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>재연마 일일생산 보고  ─  2026년 10월 23일  (2026-10-23 07:59 생성 · 속보값)</t>
+          <t>재연마 일일생산 보고  ─  2026년 10월 23일  (2026-10-23 13:24 생성 · 속보값 · ERP 작업실적 기준)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-23 07:59   |   전일: 10월 22일   |   월평균 기준: 이전 작업일 14일 평균   |   10월 누적 작업일: 15일</t>
+          <t>생성: 2026-10-23 13:24   |   전일: 10월 22일   |   월평균 기준: 이전 작업일 14일 평균   |   10월 누적 작업일: 15일</t>
         </is>
       </c>
     </row>
@@ -670,244 +659,197 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FAST GRIND  수량 (개)</t>
+          <t>NC 양품 (개)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-35</v>
+        <v>-14</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.35</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>42.1</v>
+        <v>67</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-42.07142857142857</v>
+        <v>-41</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.6119402985074627</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FAST GRIND  가공시간 (초)</t>
+          <t>NC 불량 (개)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>12025</v>
+        <v>1</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-12025</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>9844.299999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-9844.285714285714</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>0:00:00</t>
-        </is>
-      </c>
+      <c r="I5" s="10" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>GX7  수량 (개)</t>
+          <t>합계  수량 (개, 양품+불량)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>-15</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.8823529411764706</v>
+        <v>-0.3658536585365854</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>26.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-24.5</v>
+        <v>-41.57142857142857</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.9245283018867925</v>
+        <v>-0.6152219873150105</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>GX7  가공시간 (초)</t>
+          <t>합계  가공시간 (초, 추정)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>828</v>
+        <v>8439</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7430</v>
+        <v>13563</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-6602</v>
+        <v>-5124</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.8885598923283984</v>
+        <v>-0.3777925237779252</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>8910.1</v>
+        <v>17914.7</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-8082.142857142857</v>
+        <v>-9475.714285714286</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.9070721970146383</v>
+        <v>-0.5289347144805149</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:13:48</t>
+          <t>2:20:39 (표준공수 추정)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>합계  수량 (개)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>-50</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.9615384615384616</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>-66.57142857142857</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>-0.9708333333333333</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>합계  가공시간 (초)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>828</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>19455</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>-18627</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.9574402467232074</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>18754.4</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>-17926.42857142857</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>-0.9558504277085031</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>0:13:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>합계  금액</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>-50</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.9615384615384616</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>-66.57142857142857</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>-0.9708333333333333</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
           <t>10월 누적  (15일 / 23일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>962</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>263390</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>962</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="n">
+        <v>964</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>972</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>259245</v>
+      </c>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>양품</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>불량</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>가공시간(초, 추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>※ 기준: ERP 생산실적 「작업실적」 중 공정 NC (FAST GRIND · GX7 합계, 장비 구분 없음 — 2026-10-23 결정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>※ 가공시간: 품목별 표준공수(재연마_표준공수DB_2022-2026, 개당 중앙값) × 수량으로 낸 추정값입니다. 실측 가공시간이 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>※ 금액 항목은 ERP 가격 정보를 보고서에 싣지 않는 원칙에 따라 뺐습니다. 2026-10-22 까지의 보고서는 엑셀 작업일지 기준입니다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -919,233 +861,594 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>작업 상세  ─  2026년 10월 23일</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>■ FAST GRIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+          <t>작업 상세  ─  2026년 10월 23일  (ERP 작업실적 · 공정 NC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>■ NC (FAST GRIND · GX7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>작업지시</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>소재</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>각도/R</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>양품</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>불량</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>표준(초/개)</t>
+        </is>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
+      <c r="O3" s="17" t="inlineStr">
+        <is>
+          <t>관리번호</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>형상</t>
+      <c r="A4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>2610140001</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr"/>
+      <c r="I4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>0:06:55</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>2610140006</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr"/>
+      <c r="I5" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>2490</v>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>0:41:30</t>
+        </is>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>2610120024</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr"/>
+      <c r="I6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>0:06:55</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>2610210007</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>코팅</t>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="20" t="n">
+          <t>비코팅</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr"/>
+      <c r="I7" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>2080</v>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>0:34:40</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>2610210006</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>비코팅</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>볼</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>뮤</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>828</v>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>0:13:48</t>
+      <c r="J8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>301</v>
+      </c>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="n">
+        <v>301</v>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>0:05:01</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-11</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>GX7 소계</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>828</v>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>0:13:48</t>
-        </is>
-      </c>
+      <c r="A9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>2610060012</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>11.8mm</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>330</v>
+      </c>
+      <c r="L9" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>330</v>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>0:05:30</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>2610150001</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>비코팅</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>301</v>
+      </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="n">
+        <v>2408</v>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>0:40:08</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>NC 소계</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="13" t="n">
+        <v>8439</v>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>2:20:39</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/wiki/reports/daily/2026-10-23_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-23_일일보고.xlsx
@@ -594,14 +594,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>재연마 일일생산 보고  ─  2026년 10월 23일  (2026-10-23 13:24 생성 · 속보값 · ERP 작업실적 기준)</t>
+          <t>재연마 일일생산 보고  ─  2026년 10월 23일  (2026-10-23 16:00 생성 · 속보값 · ERP 작업실적 기준)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-23 13:24   |   전일: 10월 22일   |   월평균 기준: 이전 작업일 14일 평균   |   10월 누적 작업일: 15일</t>
+          <t>생성: 2026-10-23 16:00   |   전일: 10월 22일   |   월평균 기준: 이전 작업일 14일 평균   |   10월 누적 작업일: 15일</t>
         </is>
       </c>
     </row>
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>40</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.35</v>
+        <v>-0.1</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>67</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-41</v>
+        <v>-31</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.6119402985074627</v>
+        <v>-0.4626865671641791</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -721,25 +721,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>41</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.3658536585365854</v>
+        <v>-0.1219512195121951</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-41.57142857142857</v>
+        <v>-31.57142857142857</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.6152219873150105</v>
+        <v>-0.46723044397463</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -750,29 +750,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>8439</v>
+        <v>12399</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>13563</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-5124</v>
+        <v>-1164</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.3777925237779252</v>
+        <v>-0.08582172085821721</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>17914.7</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-9475.714285714286</v>
+        <v>-5515.714285714286</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.5289347144805149</v>
+        <v>-0.3078873711155236</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>2:20:39 (표준공수 추정)</t>
+          <t>3:26:39 (표준공수 추정)</t>
         </is>
       </c>
     </row>
@@ -784,16 +784,16 @@
       </c>
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="n">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>8</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>259245</v>
+        <v>263205</v>
       </c>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1104,22 +1104,22 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>2610120024</t>
+          <t>2610210007</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>볼</t>
+          <t>평</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>12mm</t>
+          <t>10mm</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
@@ -1129,18 +1129,18 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>비코팅</t>
         </is>
       </c>
       <c r="H6" s="18" t="inlineStr"/>
       <c r="I6" s="20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>415</v>
+        <v>260</v>
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="M6" s="20" t="n">
-        <v>415</v>
+        <v>2080</v>
       </c>
       <c r="N6" s="18" t="inlineStr">
         <is>
-          <t>0:06:55</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="O6" s="18" t="inlineStr">
         <is>
-          <t>A1023-A-9</t>
+          <t>A1023-A-1</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>2610210007</t>
+          <t>2610210006</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -1197,13 +1197,13 @@
       </c>
       <c r="H7" s="18" t="inlineStr"/>
       <c r="I7" s="20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
@@ -1211,16 +1211,16 @@
         </is>
       </c>
       <c r="M7" s="20" t="n">
-        <v>2080</v>
+        <v>301</v>
       </c>
       <c r="N7" s="18" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>0:05:01</t>
         </is>
       </c>
       <c r="O7" s="18" t="inlineStr">
         <is>
-          <t>A1023-A-1</t>
+          <t>A1023-A-11</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>2610210006</t>
+          <t>2610060012</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>평</t>
+          <t>드릴</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>10mm</t>
+          <t>11.8mm</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>비코팅</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
@@ -1274,16 +1274,16 @@
         </is>
       </c>
       <c r="M8" s="20" t="n">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>0:05:01</t>
+          <t>0:05:30</t>
         </is>
       </c>
       <c r="O8" s="18" t="inlineStr">
         <is>
-          <t>A1023-A-11</t>
+          <t>A1023-A-14</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>2610060012</t>
+          <t>2610150001</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>드릴</t>
+          <t>평</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>11.8mm</t>
+          <t>10mm</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -1318,18 +1318,18 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>비코팅</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr"/>
       <c r="I9" s="20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="M9" s="20" t="n">
-        <v>330</v>
+        <v>2408</v>
       </c>
       <c r="N9" s="18" t="inlineStr">
         <is>
-          <t>0:05:30</t>
+          <t>0:40:08</t>
         </is>
       </c>
       <c r="O9" s="18" t="inlineStr">
         <is>
-          <t>A1023-A-14</t>
+          <t>A1023-A-12</t>
         </is>
       </c>
     </row>
@@ -1356,22 +1356,22 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>2610150001</t>
+          <t>2610060009</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>평</t>
+          <t>드릴</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>10mm</t>
+          <t>10.3mm</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
@@ -1381,18 +1381,18 @@
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>비코팅</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="H10" s="18" t="inlineStr"/>
       <c r="I10" s="20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
@@ -1400,54 +1400,633 @@
         </is>
       </c>
       <c r="M10" s="20" t="n">
-        <v>2408</v>
+        <v>304</v>
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>0:40:08</t>
+          <t>0:05:04</t>
         </is>
       </c>
       <c r="O10" s="18" t="inlineStr">
         <is>
-          <t>A1023-A-12</t>
+          <t>A1023-A-16</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>2610120019</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>코너</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>R1.0</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>348</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>348</v>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>0:05:48</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>2610200001</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>코너</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>비코팅</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>256</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>256</v>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>0:04:16</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>2610210008</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>코너</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>비코팅</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>351</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>351</v>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>0:05:51</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>2610120018</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr"/>
+      <c r="I14" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>440</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="n">
+        <v>880</v>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>0:14:40</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>2610220027</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>비코팅</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr"/>
+      <c r="I15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>315</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="n">
+        <v>315</v>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>0:05:15</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>2610120025</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr"/>
+      <c r="I16" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>330</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>330</v>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>0:05:30</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>2610120024</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr"/>
+      <c r="I17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="n">
+        <v>415</v>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>0:06:55</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>2610120022</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>16mm</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>TISIN</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr"/>
+      <c r="I18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>588</v>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="n">
+        <v>588</v>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>0:09:48</t>
+        </is>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>2610120023</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>16mm</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>초경</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr"/>
+      <c r="I19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>588</v>
+      </c>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="n">
+        <v>588</v>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
+        <is>
+          <t>0:09:48</t>
+        </is>
+      </c>
+      <c r="O19" s="18" t="inlineStr">
+        <is>
+          <t>A1023-A-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>NC 소계</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="J11" s="13" t="n">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="J20" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="13" t="n">
-        <v>8439</v>
-      </c>
-      <c r="N11" s="12" t="inlineStr">
-        <is>
-          <t>2:20:39</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="13" t="n">
+        <v>12399</v>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>3:26:39</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
